--- a/resources/templates/standard/K1200-05.xlsx
+++ b/resources/templates/standard/K1200-05.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="90">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>협력업체 체제 평가표</t>
   </si>
@@ -948,12 +951,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -974,20 +979,20 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1119,7 +1124,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
@@ -1138,13 +1143,13 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
       <c r="E6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
@@ -1153,7 +1158,7 @@
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
@@ -1162,7 +1167,7 @@
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
@@ -1171,7 +1176,7 @@
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
       <c r="Z6" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
@@ -1323,12 +1328,12 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="15"/>
@@ -1341,7 +1346,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
@@ -1355,16 +1360,16 @@
       <c r="Y11" s="15"/>
       <c r="Z11" s="15"/>
       <c r="AA11" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD11" s="16"/>
       <c r="AE11" s="16"/>
       <c r="AF11" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG11" s="16"/>
     </row>
@@ -1384,19 +1389,19 @@
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
       <c r="S12" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
       <c r="W12" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X12" s="17"/>
       <c r="Y12" s="17"/>
@@ -1411,12 +1416,12 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
@@ -1429,19 +1434,19 @@
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
       <c r="O13" s="20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P13" s="20"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20"/>
       <c r="S13" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T13" s="20"/>
       <c r="U13" s="20"/>
       <c r="V13" s="20"/>
       <c r="W13" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
@@ -1451,7 +1456,7 @@
       </c>
       <c r="AB13" s="21"/>
       <c r="AC13" s="22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD13" s="22"/>
       <c r="AE13" s="22"/>
@@ -1463,7 +1468,7 @@
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
@@ -1476,19 +1481,19 @@
       <c r="M14" s="23"/>
       <c r="N14" s="23"/>
       <c r="O14" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P14" s="24"/>
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T14" s="25"/>
       <c r="U14" s="25"/>
       <c r="V14" s="25"/>
       <c r="W14" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X14" s="24"/>
       <c r="Y14" s="24"/>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="AB14" s="26"/>
       <c r="AC14" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD14" s="27"/>
       <c r="AE14" s="27"/>
@@ -1510,7 +1515,7 @@
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
@@ -1523,19 +1528,19 @@
       <c r="M15" s="23"/>
       <c r="N15" s="23"/>
       <c r="O15" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P15" s="24"/>
       <c r="Q15" s="24"/>
       <c r="R15" s="24"/>
       <c r="S15" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T15" s="24"/>
       <c r="U15" s="24"/>
       <c r="V15" s="24"/>
       <c r="W15" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X15" s="24"/>
       <c r="Y15" s="24"/>
@@ -1545,7 +1550,7 @@
       </c>
       <c r="AB15" s="26"/>
       <c r="AC15" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD15" s="27"/>
       <c r="AE15" s="27"/>
@@ -1557,7 +1562,7 @@
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
@@ -1570,19 +1575,19 @@
       <c r="M16" s="23"/>
       <c r="N16" s="23"/>
       <c r="O16" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P16" s="24"/>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T16" s="24"/>
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X16" s="24"/>
       <c r="Y16" s="24"/>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="AB16" s="26"/>
       <c r="AC16" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD16" s="27"/>
       <c r="AE16" s="27"/>
@@ -1604,7 +1609,7 @@
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
@@ -1617,19 +1622,19 @@
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
       <c r="O17" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
       <c r="S17" s="24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T17" s="24"/>
       <c r="U17" s="24"/>
       <c r="V17" s="24"/>
       <c r="W17" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X17" s="24"/>
       <c r="Y17" s="24"/>
@@ -1639,7 +1644,7 @@
       </c>
       <c r="AB17" s="26"/>
       <c r="AC17" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD17" s="27"/>
       <c r="AE17" s="27"/>
@@ -1651,7 +1656,7 @@
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="23"/>
@@ -1664,19 +1669,19 @@
       <c r="M18" s="23"/>
       <c r="N18" s="23"/>
       <c r="O18" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
       <c r="R18" s="25"/>
       <c r="S18" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T18" s="25"/>
       <c r="U18" s="25"/>
       <c r="V18" s="25"/>
       <c r="W18" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X18" s="25"/>
       <c r="Y18" s="25"/>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="AB18" s="26"/>
       <c r="AC18" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD18" s="27"/>
       <c r="AE18" s="27"/>
@@ -1698,7 +1703,7 @@
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="23"/>
       <c r="F19" s="23"/>
@@ -1711,19 +1716,19 @@
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P19" s="24"/>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T19" s="24"/>
       <c r="U19" s="24"/>
       <c r="V19" s="24"/>
       <c r="W19" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X19" s="24"/>
       <c r="Y19" s="24"/>
@@ -1733,7 +1738,7 @@
       </c>
       <c r="AB19" s="26"/>
       <c r="AC19" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD19" s="27"/>
       <c r="AE19" s="27"/>
@@ -1745,7 +1750,7 @@
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
@@ -1758,19 +1763,19 @@
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
       <c r="O20" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P20" s="24"/>
       <c r="Q20" s="24"/>
       <c r="R20" s="24"/>
       <c r="S20" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T20" s="24"/>
       <c r="U20" s="24"/>
       <c r="V20" s="24"/>
       <c r="W20" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X20" s="24"/>
       <c r="Y20" s="24"/>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="AB20" s="26"/>
       <c r="AC20" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD20" s="27"/>
       <c r="AE20" s="27"/>
@@ -1792,7 +1797,7 @@
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
@@ -1805,19 +1810,19 @@
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P21" s="29"/>
       <c r="Q21" s="29"/>
       <c r="R21" s="29"/>
       <c r="S21" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T21" s="29"/>
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X21" s="29"/>
       <c r="Y21" s="29"/>
@@ -1827,7 +1832,7 @@
       </c>
       <c r="AB21" s="30"/>
       <c r="AC21" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD21" s="31"/>
       <c r="AE21" s="31"/>
@@ -1836,12 +1841,12 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
@@ -1854,19 +1859,19 @@
       <c r="M22" s="32"/>
       <c r="N22" s="32"/>
       <c r="O22" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P22" s="20"/>
       <c r="Q22" s="20"/>
       <c r="R22" s="20"/>
       <c r="S22" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
       <c r="V22" s="20"/>
       <c r="W22" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
@@ -1876,7 +1881,7 @@
       </c>
       <c r="AB22" s="21"/>
       <c r="AC22" s="22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD22" s="22"/>
       <c r="AE22" s="22"/>
@@ -1888,7 +1893,7 @@
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
@@ -1901,19 +1906,19 @@
       <c r="M23" s="23"/>
       <c r="N23" s="23"/>
       <c r="O23" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
       <c r="R23" s="24"/>
       <c r="S23" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T23" s="24"/>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
       <c r="W23" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X23" s="24"/>
       <c r="Y23" s="24"/>
@@ -1923,7 +1928,7 @@
       </c>
       <c r="AB23" s="26"/>
       <c r="AC23" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD23" s="27"/>
       <c r="AE23" s="27"/>
@@ -1935,7 +1940,7 @@
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="23"/>
       <c r="F24" s="23"/>
@@ -1948,19 +1953,19 @@
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
       <c r="O24" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P24" s="24"/>
       <c r="Q24" s="24"/>
       <c r="R24" s="24"/>
       <c r="S24" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T24" s="24"/>
       <c r="U24" s="24"/>
       <c r="V24" s="24"/>
       <c r="W24" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X24" s="24"/>
       <c r="Y24" s="24"/>
@@ -1970,7 +1975,7 @@
       </c>
       <c r="AB24" s="26"/>
       <c r="AC24" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD24" s="27"/>
       <c r="AE24" s="27"/>
@@ -1982,7 +1987,7 @@
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="28"/>
       <c r="F25" s="28"/>
@@ -1995,19 +2000,19 @@
       <c r="M25" s="28"/>
       <c r="N25" s="28"/>
       <c r="O25" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P25" s="29"/>
       <c r="Q25" s="29"/>
       <c r="R25" s="29"/>
       <c r="S25" s="29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T25" s="29"/>
       <c r="U25" s="29"/>
       <c r="V25" s="29"/>
       <c r="W25" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X25" s="29"/>
       <c r="Y25" s="29"/>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="AB25" s="30"/>
       <c r="AC25" s="31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AD25" s="31"/>
       <c r="AE25" s="31"/>
@@ -2026,12 +2031,12 @@
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
@@ -2044,19 +2049,19 @@
       <c r="M26" s="19"/>
       <c r="N26" s="19"/>
       <c r="O26" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P26" s="20"/>
       <c r="Q26" s="20"/>
       <c r="R26" s="20"/>
       <c r="S26" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
       <c r="V26" s="20"/>
       <c r="W26" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X26" s="20"/>
       <c r="Y26" s="20"/>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="AB26" s="21"/>
       <c r="AC26" s="22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD26" s="22"/>
       <c r="AE26" s="22"/>
@@ -2078,7 +2083,7 @@
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
@@ -2091,19 +2096,19 @@
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
       <c r="O27" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P27" s="25"/>
       <c r="Q27" s="25"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T27" s="25"/>
       <c r="U27" s="25"/>
       <c r="V27" s="25"/>
       <c r="W27" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X27" s="25"/>
       <c r="Y27" s="25"/>
@@ -2113,7 +2118,7 @@
       </c>
       <c r="AB27" s="26"/>
       <c r="AC27" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD27" s="27"/>
       <c r="AE27" s="27"/>
@@ -2125,7 +2130,7 @@
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
@@ -2138,19 +2143,19 @@
       <c r="M28" s="33"/>
       <c r="N28" s="33"/>
       <c r="O28" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P28" s="24"/>
       <c r="Q28" s="24"/>
       <c r="R28" s="24"/>
       <c r="S28" s="24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T28" s="24"/>
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X28" s="24"/>
       <c r="Y28" s="24"/>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="AB28" s="26"/>
       <c r="AC28" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD28" s="27"/>
       <c r="AE28" s="27"/>
@@ -2172,7 +2177,7 @@
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -2185,19 +2190,19 @@
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
       <c r="O29" s="24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P29" s="24"/>
       <c r="Q29" s="24"/>
       <c r="R29" s="24"/>
       <c r="S29" s="24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T29" s="24"/>
       <c r="U29" s="24"/>
       <c r="V29" s="24"/>
       <c r="W29" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X29" s="24"/>
       <c r="Y29" s="24"/>
@@ -2207,7 +2212,7 @@
       </c>
       <c r="AB29" s="26"/>
       <c r="AC29" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD29" s="27"/>
       <c r="AE29" s="27"/>
@@ -2216,12 +2221,12 @@
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
       <c r="D30" s="23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
@@ -2234,19 +2239,19 @@
       <c r="M30" s="23"/>
       <c r="N30" s="23"/>
       <c r="O30" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P30" s="24"/>
       <c r="Q30" s="24"/>
       <c r="R30" s="24"/>
       <c r="S30" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T30" s="24"/>
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X30" s="24"/>
       <c r="Y30" s="24"/>
@@ -2256,7 +2261,7 @@
       </c>
       <c r="AB30" s="26"/>
       <c r="AC30" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD30" s="27"/>
       <c r="AE30" s="27"/>
@@ -2268,7 +2273,7 @@
       <c r="B31" s="34"/>
       <c r="C31" s="34"/>
       <c r="D31" s="23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
@@ -2281,19 +2286,19 @@
       <c r="M31" s="23"/>
       <c r="N31" s="23"/>
       <c r="O31" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P31" s="24"/>
       <c r="Q31" s="24"/>
       <c r="R31" s="24"/>
       <c r="S31" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T31" s="24"/>
       <c r="U31" s="24"/>
       <c r="V31" s="24"/>
       <c r="W31" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X31" s="24"/>
       <c r="Y31" s="24"/>
@@ -2303,7 +2308,7 @@
       </c>
       <c r="AB31" s="26"/>
       <c r="AC31" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD31" s="27"/>
       <c r="AE31" s="27"/>
@@ -2312,12 +2317,12 @@
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="35"/>
       <c r="C32" s="35"/>
       <c r="D32" s="36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E32" s="36"/>
       <c r="F32" s="36"/>
@@ -2330,19 +2335,19 @@
       <c r="M32" s="36"/>
       <c r="N32" s="36"/>
       <c r="O32" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P32" s="29"/>
       <c r="Q32" s="29"/>
       <c r="R32" s="29"/>
       <c r="S32" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="T32" s="29"/>
       <c r="U32" s="29"/>
       <c r="V32" s="29"/>
       <c r="W32" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X32" s="29"/>
       <c r="Y32" s="29"/>
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AB32" s="30"/>
       <c r="AC32" s="31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD32" s="31"/>
       <c r="AE32" s="31"/>
@@ -2361,7 +2366,7 @@
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="37"/>
       <c r="C33" s="37"/>
@@ -2403,7 +2408,7 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B34" s="39"/>
       <c r="C34" s="15"/>
